--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -646,37 +646,37 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Проверка конфигурации</t>
+          <t>Проверка динамических списков</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CheckConfig</t>
+          <t>listcheck</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Ссылочная целостность метаданных, компилируемость модулей (тонкий клиент, сервер)</t>
+          <t>Колонки таблиц форм против произвольного запроса динамического списка: поле колонки должно быть в запросе, mainTable — в тексте запроса. Компилируется и проходит CheckConfig, но падает у пользователя при первой отрисовке списка: смок открывает форму через ПолучитьФорму() и данные списка не читает.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>scripts/smoke.sh, шаг 1 (DESIGNER /CheckConfig)</t>
+          <t>scripts/listcheck.py</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>build/check-config.log — непустой лог = провал</t>
+          <t>Вывод в терминал; известные расхождения — scripts/listcheck-known.txt</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Машина — на build/ib; человек — на базах клиентов</t>
+          <t>Машина (Claude) — после каждой правки форм</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -693,32 +693,32 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Смок-тест форм</t>
+          <t>Проверка конфигурации</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>СмокТест: формы, формы на образцах и печатные формы</t>
+          <t>CheckConfig</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка).</t>
+          <t>Ссылочная целостность метаданных, компилируемость модулей (тонкий клиент, сервер)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>scripts/smoke.sh, шаг 2 (ENTERPRISE /C "СмокТест;отчёт"); интерактивно — открыть обработку СмокТест</t>
+          <t>scripts/smoke.sh, шаг 1 (DESIGNER /CheckConfig)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ПОДОЗРЕНИЕ;печатная форма;номера нет; ИТОГ;Всего=N;Ошибок=M;НаОбразцах=K;ОшибокНаОбразцах=L;ПечатныхФорм=P;ОшибокПечати=Q. Проверки проходов 2 и 3 помечены префиксами «Образец.» и «Печать.»</t>
+          <t>build/check-config.log — непустой лог = провал</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -740,42 +740,42 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Headless-первый запуск</t>
+          <t>Смок-тест форм</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>initial-fill: пустая база → заполнение → повтор → смок</t>
+          <t>СмокТест: формы, формы на образцах и печатные формы</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Обработка НачальноеЗаполнение заводит организацию, пользователей, физлица и служебного администратора из JSON (docs/DEPLOY.md). Тест: пустая база из CF; первое заполнение — success, все created=true, organizations_total и users_total &gt; 0 (визард первого запуска не откроется), слова password в result нет; industry_attributes_created=4 (образец payload — отрасль «Строительство»); повтор под созданным администратором — success, всё created=false, industry_attributes_created=0; scripts/smoke.sh на этой базе — ТЕСТЫ ПРОЙДЕНЫ.</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка).</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>scripts/initial-fill-test.sh &lt;файл.cf&gt; [каталог-базы] (по умолчанию build/ib-initial); INITIAL_FILL_NO_SMOKE=1 — без смока</t>
+          <t>scripts/smoke.sh, шаг 2 (ENTERPRISE /C "СмокТест;отчёт"); интерактивно — открыть обработку СмокТест</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>build/initial-fill-test-1.json, build/initial-fill-test-2.json (result), build/initial-fill-report.txt: СТАРТ; ПРЕДУПРЕЖДЕНИЕ;текст; ИТОГ;Успех=1|0;сводка; клиентский лог build/initial-fill-client.log</t>
+          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ПОДОЗРЕНИЕ;печатная форма;номера нет; ИТОГ;Всего=N;Ошибок=M;НаОбразцах=K;ОшибокНаОбразцах=L;ПечатныхФорм=P;ОшибокПечати=Q. Проверки проходов 2 и 3 помечены префиксами «Образец.» и «Печать.»</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Машина — на build/ib-initial из CF, собранного из обновлённой build/ib; человек — визард глазами на пустой базе (пароль tinycio-1c показывается один раз)</t>
+          <t>Машина — на build/ib; человек — на базах клиентов</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Да — пересоздаёт build/ib-initial; build/ib не трогает. Пароли теста случайные, во временном payload с правами 600, удаляется</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -787,45 +787,45 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Жизненный цикл документов</t>
+          <t>Headless-первый запуск</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: девять сценариев в транзакции с откатом</t>
+          <t>initial-fill: пустая база → заполнение → повтор → смок</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта.</t>
+          <t>Обработка НачальноеЗаполнение заводит организацию, пользователей, физлица и служебного администратора из JSON (docs/DEPLOY.md). Тест: пустая база из CF; первое заполнение — success, все created=true, organizations_total и users_total &gt; 0 (визард первого запуска не откроется), слова password в result нет; industry_attributes_created=4 (образец payload — отрасль «Строительство»); повтор под созданным администратором — success, всё created=false, industry_attributes_created=0; scripts/smoke.sh на этой базе — ТЕСТЫ ПРОЙДЕНЫ.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>scripts/doctests.sh [каталог-базы] (ENTERPRISE /C "ТестыДокументов;отчёт"); интерактивно — открыть обработку ТестыДокументов</t>
+          <t>scripts/initial-fill-test.sh &lt;файл.cf&gt; [каталог-базы] (по умолчанию build/ib-initial); INITIAL_FILL_NO_SMOKE=1 — без смока</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>build/doctests-report.txt: СТАРТ;Сценариев=N; ОК;сценарий;что проверено; ОШИБКА;сценарий;описание (с сообщениями из ОбработкаПроведения); ПРОПУСК;сценарий;причина; ИТОГ;Сценариев=N;Ошибок=M;Пропущено=K. Клиентский лог build/doctests-client.log</t>
+          <t>build/initial-fill-test-1.json, build/initial-fill-test-2.json (result), build/initial-fill-report.txt: СТАРТ; ПРЕДУПРЕЖДЕНИЕ;текст; ИТОГ;Успех=1|0;сводка; клиентский лог build/initial-fill-client.log</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Машина — на build/ib; человек — на копиях баз клиентов как приёмочный контроль (данные не меняются)</t>
+          <t>Машина — на build/ib-initial из CF, собранного из обновлённой build/ib; человек — визард глазами на пустой базе (пароль tinycio-1c показывается один раз)</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Нет — транзакция каждого сценария откатывается</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
+          <t>Да — пересоздаёт build/ib-initial; build/ib не трогает. Пароли теста случайные, во временном payload с правами 600, удаляется</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Реализован</t>
         </is>
@@ -834,55 +834,102 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Жизненный цикл документов</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ТестыДокументов: девять сценариев в транзакции с откатом</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>scripts/doctests.sh [каталог-базы] (ENTERPRISE /C "ТестыДокументов;отчёт"); интерактивно — открыть обработку ТестыДокументов</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>build/doctests-report.txt: СТАРТ;Сценариев=N; ОК;сценарий;что проверено; ОШИБКА;сценарий;описание (с сообщениями из ОбработкаПроведения); ПРОПУСК;сценарий;причина; ИТОГ;Сценариев=N;Ошибок=M;Пропущено=K. Клиентский лог build/doctests-client.log</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Машина — на build/ib; человек — на копиях баз клиентов как приёмочный контроль (данные не меняются)</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Нет — транзакция каждого сценария откатывается</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Реализован</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Сценарные UI-тесты</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Тест-клиент платформы / Vanessa Automation</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Клиентская логика: обработчики ПриИзменении, подборы, команды форм, сквозные сценарии</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>План: 1cv8 /TESTCLIENT + управляющий сценарий</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Машина готовит сценарии, человек контролирует прогон</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Да — только на копии базы</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>План: при появлении ломающихся клиентских сценариев</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Обновлено: 2026-09-08. Источник: docs/TESTING.md (регламент)</t>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Обновлено: 2026-09-09. Источник: docs/TESTING.md</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1321,6 +1368,18 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>Каждый сценарий уровня 3 выполняется в транзакции, которую обработка откатывает и после успеха, и после ошибки; фиксации нет намеренно. Поэтому прогон можно запускать на копии базы клиента. Данные сценария (контрагент, склад, касса, счёт, номенклатура) заводятся заново внутри транзакции с пометкой «Тест уровня 3»; из базы берутся только организация и валюта регламентированного учёта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Известные расхождения проверки списков</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>scripts/listcheck-known.txt хранит принятые расхождения колонок и запросов динамических списков (наследие перенесённых форм). Новое расхождение — ошибка: разбирается до сдачи, в файл попадает только вместе с причиной в docs/TECHDEBT.md.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: девять сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 13 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован</t>
+          <t>Реализован; новые сценарии E1 ожидают прогона на обновлённой базе 2.0.15.2</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-09. Источник: docs/TESTING.md</t>
+          <t>Обновлено: 2026-09-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 13 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 15 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; новые сценарии E1 ожидают прогона на обновлённой базе 2.0.15.2</t>
+          <t>Реализован; пять сценариев техкарт ожидают прогона на обновлённой базе 2.0.15.3</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; пять сценариев техкарт ожидают прогона на обновлённой базе 2.0.15.3</t>
+          <t>Реализован; пять сценариев техкарт ожидают прогона на обновлённой базе 2.0.15.4</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; пять сценариев техкарт ожидают прогона на обновлённой базе 2.0.15.4</t>
+          <t>Реализован; пять сценариев техкарт ожидают прогона на обновлённой базе 2.0.15.5</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; пять сценариев техкарт ожидают прогона на обновлённой базе 2.0.15.5</t>
+          <t>Реализован; пять сценариев техкарт ожидают прогона на обновлённой базе 2.0.15.6</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 15 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 16 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; пять сценариев техкарт ожидают прогона на обновлённой базе 2.0.15.6</t>
+          <t>Реализован; 16 сценариев пройдены на обновлённой build/ib 2.0.15.7: ошибок 0, пропусков 0; ручная проверка поля E2 остаётся</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 16 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 17 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; 16 сценариев пройдены на обновлённой build/ib 2.0.15.7: ошибок 0, пропусков 0; ручная проверка поля E2 остаётся</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8</t>
         </is>
       </c>
     </row>
@@ -925,10 +925,11 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md</t>
+          <t>Обновлено: 2026-09-12. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2601,24 +2602,46 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Документ.КоммерческоеПредложение</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Devis A4</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>scripts/fixtures.sh заводит образец автоматически</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Образец заводится прогоном</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Обновлено: 2026-08-27. Источник: docs/TESTING.md, раздел «План: покрытие печати образцами данных».</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="n"/>
       <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Обновлено: 2026-09-12. Источник: docs/TESTING.md, раздел «План: покрытие печати образцами данных».</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>scripts/fixtures.sh заводит образец автоматически</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Образец заводится прогоном</t>
         </is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 17 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 18 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-12. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение</t>
+          <t>Обновлено: 2026-09-13. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 18 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 19 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-13. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента</t>
+          <t>Обновлено: 2026-09-13. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 19 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 20 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.14</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-13. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство</t>
+          <t>Обновлено: 2026-09-13. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 20 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 21 сценарий в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.14</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.14; E7: 21-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.15</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.14; E7: 21-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.15</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 21 сценарий в транзакции с откатом</t>
+          <t>ТестыДокументов: 22 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.20</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-13. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство</t>
+          <t>Обновлено: 2026-09-14. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.20</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 22 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 23 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). СтадииЗаказа явно выключает константу автовыпуска.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.21</t>
         </is>
       </c>
     </row>
@@ -925,11 +925,10 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-14. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство</t>
+          <t>Обновлено: 2026-09-14. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.21</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 23 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 24 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). СтадииЗаказа явно выключает константу автовыпуска.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. СтадииЗаказа явно выключает константу автовыпуска.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.23</t>
         </is>
       </c>
     </row>
@@ -925,10 +925,11 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-14. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке</t>
+          <t>Обновлено: 2026-09-14. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.23</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка).</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка). Демо-набор контура 2mzl и торговли (E11): scripts/fixtures.sh --demo заводит заказы на производство на каждой стадии, статусы продаж, КП, договоров, лидов и заявок — ручная приёмка и скриншоты инструкций.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 24 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 25 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. СтадииЗаказа явно выключает константу автовыпуска.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25-й сценарий пройден на копии build/ib 2.0.15.23 с частично загруженными модулями, ожидает полного обновления до 2.0.15.24</t>
         </is>
       </c>
     </row>
@@ -925,10 +925,11 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-14. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск</t>
+          <t>Обновлено: 2026-09-14. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25-й сценарий пройден на копии build/ib 2.0.15.23 с частично загруженными модулями, ожидает полного обновления до 2.0.15.24</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -691,81 +691,81 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Проверка конфигурации</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>CheckConfig</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Ссылочная целостность метаданных, компилируемость модулей (тонкий клиент, сервер)</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>scripts/smoke.sh, шаг 1 (DESIGNER /CheckConfig)</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>build/check-config.log — непустой лог = провал</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Машина — на build/ib; человек — на базах клиентов</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Сверка полей запросов</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>queryfields</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Поля документов и справочников в текстах запросов модулей против реквизитов и табличных частей .mdo: запрос с несуществующим полем падает только при выполнении, в клиентском обработчике (панель «Детали» по активации строки) его не видят ни CheckConfig, ни смок</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>scripts/queryfields.py; известные расхождения — scripts/queryfields-known.txt, --update-known</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Стдвывод: поле, таблица, модуль и строка; код возврата 1 при новых расхождениях</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Машина — ai-test и ai-final-check при правке src/cf</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Реализован</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Реализован 2026-09-14 (2.0.15.25): нашёл четыре панели «Детали» списков с несуществующими полями</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Смок-тест форм</t>
+          <t>Проверка конфигурации</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>СмокТест: формы, формы на образцах и печатные формы</t>
+          <t>CheckConfig</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка). Демо-набор контура 2mzl и торговли (E11): scripts/fixtures.sh --demo заводит заказы на производство на каждой стадии, статусы продаж, КП, договоров, лидов и заявок — ручная приёмка и скриншоты инструкций.</t>
+          <t>Ссылочная целостность метаданных, компилируемость модулей (тонкий клиент, сервер)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>scripts/smoke.sh, шаг 2 (ENTERPRISE /C "СмокТест;отчёт"); интерактивно — открыть обработку СмокТест</t>
+          <t>scripts/smoke.sh, шаг 1 (DESIGNER /CheckConfig)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ПОДОЗРЕНИЕ;печатная форма;номера нет; ИТОГ;Всего=N;Ошибок=M;НаОбразцах=K;ОшибокНаОбразцах=L;ПечатныхФорм=P;ОшибокПечати=Q. Проверки проходов 2 и 3 помечены префиксами «Образец.» и «Печать.»</t>
+          <t>build/check-config.log — непустой лог = провал</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -787,42 +787,42 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Headless-первый запуск</t>
+          <t>Смок-тест форм</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>initial-fill: пустая база → заполнение → повтор → смок</t>
+          <t>СмокТест: формы, формы на образцах и печатные формы</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Обработка НачальноеЗаполнение заводит организацию, пользователей, физлица и служебного администратора из JSON (docs/DEPLOY.md). Тест: пустая база из CF; первое заполнение — success, все created=true, organizations_total и users_total &gt; 0 (визард первого запуска не откроется), слова password в result нет; industry_attributes_created=4 (образец payload — отрасль «Строительство»); повтор под созданным администратором — success, всё created=false, industry_attributes_created=0; scripts/smoke.sh на этой базе — ТЕСТЫ ПРОЙДЕНЫ.</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка). Демо-набор контура 2mzl и торговли (E11): scripts/fixtures.sh --demo заводит заказы на производство на каждой стадии, статусы продаж, КП, договоров, лидов и заявок — ручная приёмка и скриншоты инструкций.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>scripts/initial-fill-test.sh &lt;файл.cf&gt; [каталог-базы] (по умолчанию build/ib-initial); INITIAL_FILL_NO_SMOKE=1 — без смока</t>
+          <t>scripts/smoke.sh, шаг 2 (ENTERPRISE /C "СмокТест;отчёт"); интерактивно — открыть обработку СмокТест</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>build/initial-fill-test-1.json, build/initial-fill-test-2.json (result), build/initial-fill-report.txt: СТАРТ; ПРЕДУПРЕЖДЕНИЕ;текст; ИТОГ;Успех=1|0;сводка; клиентский лог build/initial-fill-client.log</t>
+          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ПОДОЗРЕНИЕ;печатная форма;номера нет; ИТОГ;Всего=N;Ошибок=M;НаОбразцах=K;ОшибокНаОбразцах=L;ПечатныхФорм=P;ОшибокПечати=Q. Проверки проходов 2 и 3 помечены префиксами «Образец.» и «Печать.»</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Машина — на build/ib-initial из CF, собранного из обновлённой build/ib; человек — визард глазами на пустой базе (пароль tinycio-1c показывается один раз)</t>
+          <t>Машина — на build/ib; человек — на базах клиентов</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Да — пересоздаёт build/ib-initial; build/ib не трогает. Пароли теста случайные, во временном payload с правами 600, удаляется</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -834,99 +834,147 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Жизненный цикл документов</t>
+          <t>Headless-первый запуск</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 25 сценариев в транзакции с откатом</t>
+          <t>initial-fill: пустая база → заполнение → повтор → смок</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска.</t>
+          <t>Обработка НачальноеЗаполнение заводит организацию, пользователей, физлица и служебного администратора из JSON (docs/DEPLOY.md). Тест: пустая база из CF; первое заполнение — success, все created=true, organizations_total и users_total &gt; 0 (визард первого запуска не откроется), слова password в result нет; industry_attributes_created=4 (образец payload — отрасль «Строительство»); повтор под созданным администратором — success, всё created=false, industry_attributes_created=0; scripts/smoke.sh на этой базе — ТЕСТЫ ПРОЙДЕНЫ.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>scripts/doctests.sh [каталог-базы] (ENTERPRISE /C "ТестыДокументов;отчёт"); интерактивно — открыть обработку ТестыДокументов</t>
+          <t>scripts/initial-fill-test.sh &lt;файл.cf&gt; [каталог-базы] (по умолчанию build/ib-initial); INITIAL_FILL_NO_SMOKE=1 — без смока</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>build/doctests-report.txt: СТАРТ;Сценариев=N; ОК;сценарий;что проверено; ОШИБКА;сценарий;описание (с сообщениями из ОбработкаПроведения); ПРОПУСК;сценарий;причина; ИТОГ;Сценариев=N;Ошибок=M;Пропущено=K. Клиентский лог build/doctests-client.log</t>
+          <t>build/initial-fill-test-1.json, build/initial-fill-test-2.json (result), build/initial-fill-report.txt: СТАРТ; ПРЕДУПРЕЖДЕНИЕ;текст; ИТОГ;Успех=1|0;сводка; клиентский лог build/initial-fill-client.log</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Машина — на build/ib; человек — на копиях баз клиентов как приёмочный контроль (данные не меняются)</t>
+          <t>Машина — на build/ib-initial из CF, собранного из обновлённой build/ib; человек — визард глазами на пустой базе (пароль tinycio-1c показывается один раз)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Нет — транзакция каждого сценария откатывается</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок</t>
+          <t>Да — пересоздаёт build/ib-initial; build/ib не трогает. Пароли теста случайные, во временном payload с правами 600, удаляется</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Реализован</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Жизненный цикл документов</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ТестыДокументов: 25 сценариев в транзакции с откатом</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>scripts/doctests.sh [каталог-базы] (ENTERPRISE /C "ТестыДокументов;отчёт"); интерактивно — открыть обработку ТестыДокументов</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>build/doctests-report.txt: СТАРТ;Сценариев=N; ОК;сценарий;что проверено; ОШИБКА;сценарий;описание (с сообщениями из ОбработкаПроведения); ПРОПУСК;сценарий;причина; ИТОГ;Сценариев=N;Ошибок=M;Пропущено=K. Клиентский лог build/doctests-client.log</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Машина — на build/ib; человек — на копиях баз клиентов как приёмочный контроль (данные не меняются)</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Нет — транзакция каждого сценария откатывается</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Сценарные UI-тесты</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Тест-клиент платформы / Vanessa Automation</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Клиентская логика: обработчики ПриИзменении, подборы, команды форм, сквозные сценарии</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>План: 1cv8 /TESTCLIENT + управляющий сценарий</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Машина готовит сценарии, человек контролирует прогон</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Да — только на копии базы</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>План: при появлении ломающихся клиентских сценариев</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Обновлено: 2026-09-14. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор</t>
         </is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание номенклатуры, печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, «Производство» по предложению с продукцией и «Оба» при включённой опции «Производство», представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -972,7 +972,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,12 +891,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 25 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 26 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи).</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,12 +891,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 26 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 27 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.</t>
         </is>
       </c>
     </row>
@@ -972,10 +972,11 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-14. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор</t>
+          <t>Обновлено: 2026-09-15. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,12 +891,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 27 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 28 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,12 +891,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 28 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 29 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,12 +891,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 29 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 30 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,12 +891,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 30 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 31 сценарий в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT.</t>
         </is>
       </c>
     </row>
@@ -972,11 +972,10 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-15. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор</t>
+          <t>Обновлено: 2026-09-17. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 31 сценарий в транзакции с откатом</t>
+          <t>ТестыДокументов: 32 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,12 +891,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 32 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 34 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева).</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -975,7 +975,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-17. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор</t>
+          <t>Обновлено: 2026-09-19. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала последним шагом; ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева).</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -975,7 +975,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-19. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор</t>
+          <t>Обновлено: 2026-09-20. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md)</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 34 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 35 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -975,7 +975,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-20. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md)</t>
+          <t>Обновлено: 2026-09-20. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же)</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 35 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 36 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -975,7 +975,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-20. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же)</t>
+          <t>Обновлено: 2026-09-21. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md)</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто.</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-21. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md)</t>
+          <t>Обновлено: 2026-09-21. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»)</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка.</t>
         </is>
       </c>
     </row>
@@ -972,6 +972,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка. S7 (2.0.15.49): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.49 — 1 ошибка (НастройкиПрограммы, базовая линия), АРМПроизводство с шагами S7 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто (первый прогон поймал вызов метода формы в общем модуле — tiny1C bsl-020); подбор на клиенте — ручная приёмка.</t>
         </is>
       </c>
     </row>
@@ -972,11 +972,10 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-21. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»)</t>
+          <t>Обновлено: 2026-09-22. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md)</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,6 +116,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1443,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -2105,9 +2108,43 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Источник: ПропускаемыеФормы() в модуле формы обработки СмокТест. Первый полный прогон: 421 форма, 48 ошибок, из них 37 пропусков и 11 дефектов.</t>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Печать.Документ.ЗаказПоставщику.ЗапросКотировок</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Не исключение форм, а список ПечатныеФормыБезНомера(): запрос котировок номера нашего документа не печатает - в шапке макета заголовок и стороны</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Печать.Документ.ЗаказПоставщику.ЗапросКотировокСФото</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>То же, вариант с фото</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Источник: ПропускаемыеФормы() и ПечатныеФормыБезНомера() обработки СмокТест. Первый полный прогон: 421 форма, 48 ошибок, из них 37 пропусков и 11 дефектов.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 36 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 41 сценарий в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-22. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md)</t>
+          <t>Обновлено: 2026-09-24. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md)</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 41 сценарий в транзакции с откатом</t>
+          <t>ТестыДокументов: 38 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-24. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md)</t>
+          <t>Обновлено: 2026-09-28. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 38 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 39 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-28. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара.</t>
+          <t>Обновлено: 2026-09-29. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Реестр тестов" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Регламент релиза" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Правила" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Пропуски смока" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Покрытие печати" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр тестов" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Регламент релиза" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пропуски смока" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие печати" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -800,12 +800,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>СмокТест: формы, формы на образцах и печатные формы</t>
+          <t>СмокТест: формы, формы на образцах, печатные формы и отчёты</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка). Демо-набор контура 2mzl и торговли (E11): scripts/fixtures.sh --demo заводит заказы на производство на каждой стадии, статусы продаж, КП, договоров, лидов и заявок — ручная приёмка и скриншоты инструкций.</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка). Демо-набор контура 2mzl и торговли (E11): scripts/fixtures.sh --demo заводит заказы на производство на каждой стадии, статусы продаж, КП, договоров, лидов и заявок — ручная приёмка и скриншоты инструкций. Проход 4 (с 2.0.16.4): каждый вариант каждого отчёта с основной схемой компоновки формируется СкомпоноватьРезультат с заполненными пустыми параметрами — ловит «Поле не найдено» в вариантах настроек (tiny1C query-006); известные ошибки — ПропускаемыеВариантыОтчетов и лист «Пропуски смока».</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -975,6 +975,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -1446,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -2145,6 +2146,57 @@
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Источник: ПропускаемыеФормы() и ПечатныеФормыБезНомера() обработки СмокТест. Первый полный прогон: 421 форма, 48 ошибок, из них 37 пропусков и 11 дефектов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Отчет.ПросроченныеДолгиПоставщиков.Основной</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Проход 4: вариант ссылается на поле РеализацияТоваровУслуг вне схемы (скопирован с покупательского) — чинится в этапе «Закупки» волны menu-restructure</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Отчет.ДвиженияТовара.ОтчетПоСписанию</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Проход 4: поле Склад от старого регистра ТоварыНаСкладах — чинится в этапе «Склад»</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Отчет.ОтчетПоПроводкам.ОтчетПоПроводкам</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Проход 4: поле «Количество Дт» в группировке «Заголовок» — чинится в этапе «Бухгалтерия»</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -894,12 +894,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 39 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 40 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -894,12 +894,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 40 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 41 сценарий в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -975,7 +975,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -1447,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -2152,12 +2151,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Отчет.ПросроченныеДолгиПоставщиков.Основной</t>
+          <t>Отчет.ДвиженияТовара.ОтчетПоСписанию</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Проход 4: вариант ссылается на поле РеализацияТоваровУслуг вне схемы (скопирован с покупательского) — чинится в этапе «Закупки» волны menu-restructure</t>
+          <t>Проход 4: поле Склад от старого регистра ТоварыНаСкладах — чинится в этапе «Склад»</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2169,32 +2168,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Отчет.ДвиженияТовара.ОтчетПоСписанию</t>
+          <t>Отчет.ОтчетПоПроводкам.ОтчетПоПроводкам</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Проход 4: поле Склад от старого регистра ТоварыНаСкладах — чинится в этапе «Склад»</t>
+          <t>Проход 4: поле «Количество Дт» в группировке «Заголовок» — чинится в этапе «Бухгалтерия»</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Отчет.ОтчетПоПроводкам.ОтчетПоПроводкам</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Проход 4: поле «Количество Дт» в группировке «Заголовок» — чинится в этапе «Бухгалтерия»</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -894,12 +894,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 41 сценарий в транзакции с откатом</t>
+          <t>ТестыДокументов: 42 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -894,12 +894,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 42 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 43 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1446,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -2090,6 +2090,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -2151,32 +2152,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Отчет.ДвиженияТовара.ОтчетПоСписанию</t>
+          <t>Отчет.ОтчетПоПроводкам.ОтчетПоПроводкам</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Проход 4: поле Склад от старого регистра ТоварыНаСкладах — чинится в этапе «Склад»</t>
+          <t>Проход 4: поле «Количество Дт» в группировке «Заголовок» — чинится в этапе «Бухгалтерия»</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Отчет.ОтчетПоПроводкам.ОтчетПоПроводкам</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Проход 4: поле «Количество Дт» в группировке «Заголовок» — чинится в этапе «Бухгалтерия»</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -894,12 +894,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 43 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 45 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; шесть бухотчётов формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»).</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2090,7 +2090,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; шесть бухотчётов формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе».</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Проход 4: поле «Количество Дт» в группировке «Заголовок» — чинится в этапе «Бухгалтерия»</t>
+          <t>Вариант собирает модуль менеджера (ПередКомпоновкойМакета), прямая компоновка смока его не вызывает; путь формы (ПодготовитьОтчет) на проводке проверяет сценарий МенюКазначействаИБухгалтерии (2.0.16.11)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка). Демо-набор контура 2mzl и торговли (E11): scripts/fixtures.sh --demo заводит заказы на производство на каждой стадии, статусы продаж, КП, договоров, лидов и заявок — ручная приёмка и скриншоты инструкций. Проход 4 (с 2.0.16.4): каждый вариант каждого отчёта с основной схемой компоновки формируется СкомпоноватьРезультат с заполненными пустыми параметрами — ловит «Поле не найдено» в вариантах настроек (tiny1C query-006); известные ошибки — ПропускаемыеВариантыОтчетов и лист «Пропуски смока».</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка). Демо-набор контура 2mzl и торговли (E11): scripts/fixtures.sh --demo заводит заказы на производство на каждой стадии, статусы продаж, КП, договоров, лидов и заявок — ручная приёмка и скриншоты инструкций. Проход 4 (с 2.0.16.4): каждый вариант каждого отчёта с основной схемой компоновки формируется СкомпоноватьРезультат с заполненными пустыми параметрами — ловит «Поле не найдено» в вариантах настроек (tiny1C query-006); известные ошибки — ПропускаемыеВариантыОтчетов и лист «Пропуски смока». Каждая печатная форма формируется второй раз на другом языке конфигурации (как при переключении языка в окне печати): ошибка формирования или меньше заполненных ячеек, чем на языке сеанса, — ОШИБКА (с 2.0.16.18).</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-09-29. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке.</t>
+          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -741,81 +741,81 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Проверка конфигурации</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>CheckConfig</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Ссылочная целостность метаданных, компилируемость модулей (тонкий клиент, сервер)</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>scripts/smoke.sh, шаг 1 (DESIGNER /CheckConfig)</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>build/check-config.log — непустой лог = провал</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Машина — на build/ib; человек — на базах клиентов</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Реализован</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Шрифт шапки колонок</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>colfont</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>У каждой колонки таблицы формы явный titleFont: без него интерфейс 8.5 на macOS рисует русскую шапку с разрядкой («Н о м е р»), стиль и шрифт таблицы на неё не действуют (tiny1C forms-022). --fix проставляет Style.NormalTextFont.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>scripts/colfont.py [--fix]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Вывод в терминал: форма и строка колонки без titleFont; код возврата 1, если такие есть</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Машина (Claude) — после каждой правки форм</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Нет (с --fix правит Form.form)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Реализован 2026-10-06 (2.0.16.21): 2270 колонок в 291 форме</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Смок-тест форм</t>
+          <t>Проверка конфигурации</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>СмокТест: формы, формы на образцах, печатные формы и отчёты</t>
+          <t>CheckConfig</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка). Демо-набор контура 2mzl и торговли (E11): scripts/fixtures.sh --demo заводит заказы на производство на каждой стадии, статусы продаж, КП, договоров, лидов и заявок — ручная приёмка и скриншоты инструкций. Проход 4 (с 2.0.16.4): каждый вариант каждого отчёта с основной схемой компоновки формируется СкомпоноватьРезультат с заполненными пустыми параметрами — ловит «Поле не найдено» в вариантах настроек (tiny1C query-006); известные ошибки — ПропускаемыеВариантыОтчетов и лист «Пропуски смока». Каждая печатная форма формируется второй раз на другом языке конфигурации (как при переключении языка в окне печати): ошибка формирования или меньше заполненных ячеек, чем на языке сеанса, — ОШИБКА (с 2.0.16.18).</t>
+          <t>Ссылочная целостность метаданных, компилируемость модулей (тонкий клиент, сервер)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>scripts/smoke.sh, шаг 2 (ENTERPRISE /C "СмокТест;отчёт"); интерактивно — открыть обработку СмокТест</t>
+          <t>scripts/smoke.sh, шаг 1 (DESIGNER /CheckConfig)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ПОДОЗРЕНИЕ;печатная форма;номера нет; ИТОГ;Всего=N;Ошибок=M;НаОбразцах=K;ОшибокНаОбразцах=L;ПечатныхФорм=P;ОшибокПечати=Q. Проверки проходов 2 и 3 помечены префиксами «Образец.» и «Печать.»</t>
+          <t>build/check-config.log — непустой лог = провал</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -837,42 +837,42 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Headless-первый запуск</t>
+          <t>Смок-тест форм</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>initial-fill: пустая база → заполнение → повтор → смок</t>
+          <t>СмокТест: формы, формы на образцах, печатные формы и отчёты</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Обработка НачальноеЗаполнение заводит организацию, пользователей, физлица и служебного администратора из JSON (docs/DEPLOY.md). Тест: пустая база из CF; первое заполнение — success, все created=true, organizations_total и users_total &gt; 0 (визард первого запуска не откроется), слова password в result нет; industry_attributes_created=4 (образец payload — отрасль «Строительство»); повтор под созданным администратором — success, всё created=false, industry_attributes_created=0; scripts/smoke.sh на этой базе — ТЕСТЫ ПРОЙДЕНЫ.</t>
+          <t>Проход 1: ПриСозданииНаСервере каждой формы конфигурации на новом объекте (картинки, динсписки, программное построение). Проход 2: основные формы объекта и группы, открытые с параметром Ключ по образцу из базы, — ветки, работающие только с записанным объектом; плюс неосновные формы из явного списка ДополнительныеФормыОбъектов() (формы роли ECommerce, формы единицы и упаковки). Проход 3: формирование всех печатных форм объектов из ПечатныеФормы.ОбъектыСКомандамиПечати() по образцу из базы; в тексте формы ищется номер документа-образца — если его нет, пишется ПОДОЗРЕНИЕ (пустая шапка). Демо-набор контура 2mzl и торговли (E11): scripts/fixtures.sh --demo заводит заказы на производство на каждой стадии, статусы продаж, КП, договоров, лидов и заявок — ручная приёмка и скриншоты инструкций. Проход 4 (с 2.0.16.4): каждый вариант каждого отчёта с основной схемой компоновки формируется СкомпоноватьРезультат с заполненными пустыми параметрами — ловит «Поле не найдено» в вариантах настроек (tiny1C query-006); известные ошибки — ПропускаемыеВариантыОтчетов и лист «Пропуски смока». Каждая печатная форма формируется второй раз на другом языке конфигурации (как при переключении языка в окне печати): ошибка формирования или меньше заполненных ячеек, чем на языке сеанса, — ОШИБКА (с 2.0.16.18).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>scripts/initial-fill-test.sh &lt;файл.cf&gt; [каталог-базы] (по умолчанию build/ib-initial); INITIAL_FILL_NO_SMOKE=1 — без смока</t>
+          <t>scripts/smoke.sh, шаг 2 (ENTERPRISE /C "СмокТест;отчёт"); интерактивно — открыть обработку СмокТест</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>build/initial-fill-test-1.json, build/initial-fill-test-2.json (result), build/initial-fill-report.txt: СТАРТ; ПРЕДУПРЕЖДЕНИЕ;текст; ИТОГ;Успех=1|0;сводка; клиентский лог build/initial-fill-client.log</t>
+          <t>build/smoke-report.txt: СТАРТ; ОШИБКА;что;описание; ПУСТО;печатная форма; ПРОПУСК;что;причина; ПОДОЗРЕНИЕ;печатная форма;номера нет; ИТОГ;Всего=N;Ошибок=M;НаОбразцах=K;ОшибокНаОбразцах=L;ПечатныхФорм=P;ОшибокПечати=Q. Проверки проходов 2 и 3 помечены префиксами «Образец.» и «Печать.»</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Машина — на build/ib-initial из CF, собранного из обновлённой build/ib; человек — визард глазами на пустой базе (пароль tinycio-1c показывается один раз)</t>
+          <t>Машина — на build/ib; человек — на базах клиентов</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Да — пересоздаёт build/ib-initial; build/ib не трогает. Пароли теста случайные, во временном payload с правами 600, удаляется</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -884,99 +884,147 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Жизненный цикл документов</t>
+          <t>Headless-первый запуск</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 45 сценариев в транзакции с откатом</t>
+          <t>initial-fill: пустая база → заполнение → повтор → смок</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе».</t>
+          <t>Обработка НачальноеЗаполнение заводит организацию, пользователей, физлица и служебного администратора из JSON (docs/DEPLOY.md). Тест: пустая база из CF; первое заполнение — success, все created=true, organizations_total и users_total &gt; 0 (визард первого запуска не откроется), слова password в result нет; industry_attributes_created=4 (образец payload — отрасль «Строительство»); повтор под созданным администратором — success, всё created=false, industry_attributes_created=0; scripts/smoke.sh на этой базе — ТЕСТЫ ПРОЙДЕНЫ.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>scripts/doctests.sh [каталог-базы] (ENTERPRISE /C "ТестыДокументов;отчёт"); интерактивно — открыть обработку ТестыДокументов</t>
+          <t>scripts/initial-fill-test.sh &lt;файл.cf&gt; [каталог-базы] (по умолчанию build/ib-initial); INITIAL_FILL_NO_SMOKE=1 — без смока</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>build/doctests-report.txt: СТАРТ;Сценариев=N; ОК;сценарий;что проверено; ОШИБКА;сценарий;описание (с сообщениями из ОбработкаПроведения); ПРОПУСК;сценарий;причина; ИТОГ;Сценариев=N;Ошибок=M;Пропущено=K. Клиентский лог build/doctests-client.log</t>
+          <t>build/initial-fill-test-1.json, build/initial-fill-test-2.json (result), build/initial-fill-report.txt: СТАРТ; ПРЕДУПРЕЖДЕНИЕ;текст; ИТОГ;Успех=1|0;сводка; клиентский лог build/initial-fill-client.log</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Машина — на build/ib; человек — на копиях баз клиентов как приёмочный контроль (данные не меняются)</t>
+          <t>Машина — на build/ib-initial из CF, собранного из обновлённой build/ib; человек — визард глазами на пустой базе (пароль tinycio-1c показывается один раз)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Нет — транзакция каждого сценария откатывается</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка. S7 (2.0.15.49): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.49 — 1 ошибка (НастройкиПрограммы, базовая линия), АРМПроизводство с шагами S7 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто (первый прогон поймал вызов метода формы в общем модуле — tiny1C bsl-020); подбор на клиенте — ручная приёмка.</t>
+          <t>Да — пересоздаёт build/ib-initial; build/ib не трогает. Пароли теста случайные, во временном payload с правами 600, удаляется</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Реализован</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Жизненный цикл документов</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ТестыДокументов: 45 сценариев в транзакции с откатом</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе».</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>scripts/doctests.sh [каталог-базы] (ENTERPRISE /C "ТестыДокументов;отчёт"); интерактивно — открыть обработку ТестыДокументов</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>build/doctests-report.txt: СТАРТ;Сценариев=N; ОК;сценарий;что проверено; ОШИБКА;сценарий;описание (с сообщениями из ОбработкаПроведения); ПРОПУСК;сценарий;причина; ИТОГ;Сценариев=N;Ошибок=M;Пропущено=K. Клиентский лог build/doctests-client.log</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Машина — на build/ib; человек — на копиях баз клиентов как приёмочный контроль (данные не меняются)</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Нет — транзакция каждого сценария откатывается</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка. S7 (2.0.15.49): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.49 — 1 ошибка (НастройкиПрограммы, базовая линия), АРМПроизводство с шагами S7 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто (первый прогон поймал вызов метода формы в общем модуле — tiny1C bsl-020); подбор на клиенте — ручная приёмка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Сценарные UI-тесты</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Тест-клиент платформы / Vanessa Automation</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Клиентская логика: обработчики ПриИзменении, подборы, команды форм, сквозные сценарии</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>План: 1cv8 /TESTCLIENT + управляющий сценарий</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Машина готовит сценарии, человек контролирует прогон</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Да — только на копии базы</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>План: при появлении ломающихся клиентских сценариев</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке.</t>
         </is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 45 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 46 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке.</t>
+          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 46 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 47 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md).</t>
+          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 47 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 48 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md).</t>
+          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 48 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 49 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md).</t>
+          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 49 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 50 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе».</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1022,7 +1022,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков».</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 50 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 52 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков».</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков».</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-06. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md).</t>
+          <t>Обновлено: 2026-10-07. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 52 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 55 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков».</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1022,10 +1022,11 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-07. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1).</t>
+          <t>Обновлено: 2026-10-08. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 55 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 56 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1022,11 +1022,10 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-08. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2).</t>
+          <t>Обновлено: 2026-10-08. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -1022,10 +1022,11 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-08. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3).</t>
+          <t>Обновлено: 2026-10-08. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 56 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 61 сценарий в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-08. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4).</t>
+          <t>Обновлено: 2026-10-08. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -1022,11 +1022,10 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-08. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5).</t>
+          <t>Обновлено: 2026-10-09. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 61 сценарий в транзакции с откатом</t>
+          <t>ТестыДокументов: 63 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1022,10 +1022,11 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-09. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md).</t>
+          <t>Обновлено: 2026-10-09. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 63 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 66 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1022,11 +1022,10 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-09. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44.</t>
+          <t>Обновлено: 2026-10-09. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -971,7 +971,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка. S7 (2.0.15.49): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.49 — 1 ошибка (НастройкиПрограммы, базовая линия), АРМПроизводство с шагами S7 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто (первый прогон поймал вызов метода формы в общем модуле — tiny1C bsl-020); подбор на клиенте — ручная приёмка.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка. S7 (2.0.15.49): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.49 — 1 ошибка (НастройкиПрограммы, базовая линия), АРМПроизводство с шагами S7 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто (первый прогон поймал вызов метода формы в общем модуле — tiny1C bsl-020); подбор на клиенте — ручная приёмка.; 2026-10-09: рабочее место «Управление станками» — состав опции, меню и права в СтанкиИОбслуживание</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 66 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 67 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печать Devis A4, заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 67 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 68 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка. S7 (2.0.15.49): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.49 — 1 ошибка (НастройкиПрограммы, базовая линия), АРМПроизводство с шагами S7 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто (первый прогон поймал вызов метода формы в общем модуле — tiny1C bsl-020); подбор на клиенте — ручная приёмка.; 2026-10-09: рабочее место «Управление станками» — состав опции, меню и права в СтанкиИОбслуживание</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка. S7 (2.0.15.49): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.49 — 1 ошибка (НастройкиПрограммы, базовая линия), АРМПроизводство с шагами S7 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто (первый прогон поймал вызов метода формы в общем модуле — tiny1C bsl-020); подбор на клиенте — ручная приёмка.; 2026-10-09: рабочее место «Управление станками» — состав опции, меню и права в СтанкиИОбслуживание 2.0.16.54 (2026-10-10): 68 сценариев на копии build/ib-kp, обновлённой scripts/ib-sync.sh, — 0 ошибок; смок 411 форм, 111 на образцах, 53 печатные формы, 64 варианта отчётов без ошибок, CheckConfig чисто.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-09. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md).</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка. S7 (2.0.15.49): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.49 — 1 ошибка (НастройкиПрограммы, базовая линия), АРМПроизводство с шагами S7 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто (первый прогон поймал вызов метода формы в общем модуле — tiny1C bsl-020); подбор на клиенте — ручная приёмка.; 2026-10-09: рабочее место «Управление станками» — состав опции, меню и права в СтанкиИОбслуживание 2.0.16.54 (2026-10-10): 68 сценариев на копии build/ib-kp, обновлённой scripts/ib-sync.sh, — 0 ошибок; смок 411 форм, 111 на образцах, 53 печатные формы, 64 варианта отчётов без ошибок, CheckConfig чисто.</t>
+          <t>Реализован; E2: 16 сценариев пройдены на build/ib 2.0.15.7 без ошибок и пропусков; E3: 17-й сценарий добавлен, прогон ожидает обновления build/ib до 2.0.15.8; E4: 18-й сценарий добавлен, прогон ожидает полного обновления build/ib до 2.0.15.9; E5: 19 сценариев пройдены на копии build/ib 2.0.15.13 без ошибок и пропусков; E6: 20-й сценарий пройден на копии build/ib 2.0.15.19; E7: 21 сценарий пройден на копии полностью обновлённой build/ib 2.0.15.19 без ошибок и пропусков; E8: 22 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.20 без ошибок и пропусков; E9: 23 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.21 с исправлениями 2.0.15.22 без ошибок и пропусков; E10: 24 сценария пройдены на копии полностью обновлённой build/ib 2.0.15.23 без ошибок и пропусков; E11: 25 сценариев пройдены на копии полностью обновлённой build/ib 2.0.15.24 до и после засева демо-набора без ошибок; E12.1: 27-й сценарий АРМПроизводство добавлен в 2.0.15.29, прогон ожидает полного обновления build/ib; форма рабочего места — смок и ручная приёмка под ОператорПроизводства.; E12.2: 28-й сценарий АРМЗакупки добавлен в 2.0.15.32, прогнан на копии build/ib 2.0.15.31 с платформенной копией формы; клиентская логика закладок закупок — ручная приёмка.; E12.3a: 29-й сценарий АРМВыпускОтгрузка добавлен в 2.0.15.33, прогнан на копии build/ib с платформенной копией формы и выпуска; клиентская логика закладок выпуска и отгрузок — ручная приёмка.; E12.3b: 30-й сценарий АРМПереработка добавлен в 2.0.15.34, прогнан на копии build/ib 2.0.15.33 с платформенной копией формы, документов переработки и начальной страницы; закладка «Переработка» и начальная страница оператора — ручная приёмка.; E12.4 (2.0.15.35): прогнан на копии build/ib 2.0.15.34 с платформенной копией формы и модулей — 29 из 30 (сценарий НастройкиПрограммы падает и на нетронутой базе: часовой пояс окружения, TECHDEBT), смок 398 форм и 54 печатные формы без ошибок; ширины колонок, счётчики закладок, цвета движения и кнопки на основании — ручная приёмка. 2.0.15.36: 31-й сценарий СебестоимостьПродукции — компоновка отчёта «Себестоимость продукции» и сверка с приходом регистра ТоварыВНаличии; прогон ждёт обновления build/ib из EDT. S5-B (2.0.15.45): 36 сценариев прогнаны на build/ib, обновлённой из EDT — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S9 (2.0.15.46): 36 сценариев прогнаны на build/ib, обновлённой из EDT (scripts/ib-sync.sh) — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, есть и в базовой линии), АвтовыпускПриОтгрузке и АвтовыпускПриПередаче с новыми шагами ОК; смок 398 форм и 54 печатные формы без ошибок, CheckConfig чисто. S6 (2.0.15.48): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.48 — 1 ошибка (НастройкиПрограммы: часовой пояс окружения, базовая линия), АРМПереработка с шагами S6 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто; закладка поступлений на клиенте — ручная приёмка. S7 (2.0.15.49): 36 сценариев на копии build/ib, обновлённой scripts/ib-sync.sh до 2.0.15.49 — 1 ошибка (НастройкиПрограммы, базовая линия), АРМПроизводство с шагами S7 ОК; смок 398 форм, 111 на образцах, 54 печатные формы без ошибок, CheckConfig чисто (первый прогон поймал вызов метода формы в общем модуле — tiny1C bsl-020); подбор на клиенте — ручная приёмка.; 2026-10-09: рабочее место «Управление станками» — состав опции, меню и права в СтанкиИОбслуживание 2.0.16.54 (2026-10-10): 68 сценариев на копии build/ib-kp, обновлённой scripts/ib-sync.sh, — 0 ошибок; смок 411 форм, 111 на образцах, 53 печатные формы, 64 варианта отчётов без ошибок, CheckConfig чисто. 2.0.16.55–57 (2026-10-10): по 69 сценариев на копии build/ib-kp — 0 ошибок после исправлений (первые прогоны 2.0.16.55 поймали ошибку теста и неработающее ограничение схемы СКД — tiny1C query-009); смок 411 форм, 111 на образцах, 53 печатные формы, 64 варианта отчётов без ошибок. 2.0.16.58: 69 сценариев — 0 ошибок, смок 410 форм (удалена проба планировщика) без ошибок.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6).</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 68 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 70 сценариев в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1022,10 +1022,11 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md).</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 70 сценариев в транзакции с откатом</t>
+          <t>ТестыДокументов: 71 сценарий в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени.</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели.</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки; КарточкаНоменклатуры: показатели шапки.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений).</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений). 2.0.16.62: КарточкаНоменклатуры дополнен показателями шапки карточки (ПоказателиКарточки: остаток, свободно, ниже минимума).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки; КарточкаНоменклатуры: показатели шапки.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки; КарточкаНоменклатуры: показатели шапки; КарточкаНоменклатуры: блоки карточки.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений). 2.0.16.62: КарточкаНоменклатуры дополнен показателями шапки карточки (ПоказателиКарточки: остаток, свободно, ниже минимума).</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений). 2.0.16.62: КарточкаНоменклатуры дополнен показателями шапки карточки (ПоказателиКарточки: остаток, свободно, ниже минимума). 2.0.16.63: КарточкаНоменклатуры дополнен блоками карточки (ДанныеКарточки: где используется, остатки и свободно, штрихкоды).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -946,7 +946,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки; КарточкаНоменклатуры: показатели шапки; КарточкаНоменклатуры: блоки карточки.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки; КарточкаНоменклатуры: показатели шапки; КарточкаНоменклатуры: блоки карточки; СписокНоменклатуры: подбор по назначению, запрос выбора.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений). 2.0.16.62: КарточкаНоменклатуры дополнен показателями шапки карточки (ПоказателиКарточки: остаток, свободно, ниже минимума). 2.0.16.63: КарточкаНоменклатуры дополнен блоками карточки (ДанныеКарточки: где используется, остатки и свободно, штрихкоды).</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений). 2.0.16.62: КарточкаНоменклатуры дополнен показателями шапки карточки (ПоказателиКарточки: остаток, свободно, ниже минимума). 2.0.16.63: КарточкаНоменклатуры дополнен блоками карточки (ДанныеКарточки: где используется, остатки и свободно, штрихкоды). 2.0.16.64: СписокНоменклатуры — подбор по назначению и запрос выбора; смок открывает формы подбора и выбора номенклатуры с параметрами открытия.</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 71 сценарий в транзакции с откатом</t>
+          <t>ТестыДокументов: 72 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки; КарточкаНоменклатуры: показатели шапки; КарточкаНоменклатуры: блоки карточки; СписокНоменклатуры: подбор по назначению, запрос выбора.</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки; КарточкаНоменклатуры: показатели шапки; КарточкаНоменклатуры: блоки карточки; СписокНоменклатуры: подбор по назначению, запрос выбора; ПереносСтарыхСвойств (перенос старых свойств номенклатуры в дополнительные реквизиты).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений). 2.0.16.62: КарточкаНоменклатуры дополнен показателями шапки карточки (ПоказателиКарточки: остаток, свободно, ниже минимума). 2.0.16.63: КарточкаНоменклатуры дополнен блоками карточки (ДанныеКарточки: где используется, остатки и свободно, штрихкоды). 2.0.16.64: СписокНоменклатуры — подбор по назначению и запрос выбора; смок открывает формы подбора и выбора номенклатуры с параметрами открытия.</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений). 2.0.16.62: КарточкаНоменклатуры дополнен показателями шапки карточки (ПоказателиКарточки: остаток, свободно, ниже минимума). 2.0.16.63: КарточкаНоменклатуры дополнен блоками карточки (ДанныеКарточки: где используется, остатки и свободно, штрихкоды). 2.0.16.64: СписокНоменклатуры — подбор по назначению и запрос выбора; смок открывает формы подбора и выбора номенклатуры с параметрами открытия. 2.0.16.65: ПроверитьГруппыОтбора — вид сравнения и ноль числового фильтра. 2.0.16.66: сценарий ПереносСтарыхСвойств (docs/plans/old-item-properties.md, сборка A).</t>
         </is>
       </c>
     </row>

--- a/docs/TESTS.xlsx
+++ b/docs/TESTS.xlsx
@@ -941,12 +941,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ТестыДокументов: 72 сценария в транзакции с откатом</t>
+          <t>ТестыДокументов: 73 сценария в транзакции с откатом</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки; КарточкаНоменклатуры: показатели шапки; КарточкаНоменклатуры: блоки карточки; СписокНоменклатуры: подбор по назначению, запрос выбора; ПереносСтарыхСвойств (перенос старых свойств номенклатуры в дополнительные реквизиты).</t>
+          <t>Создание, ПроверитьЗаполнение, запись и проведение ключевых документов, сверка движений по регистрам. Сценарии: Закупка (остаток, долг поставщику); Продажа (заказ → реализация по заказу → ПКО: остаток, регистр Продажи, долг покупателя закрыт, касса); ВозвратОтПокупателя (партия вернулась, продажи сторнированы, долг закрыт); ВыпускПродукции (списание сырья по техкарте, приход продукции; ПРОПУСК без ФО «Производство»); Переработка (передача и поступление из переработки: остатки у переработчика, себестоимость с услугами, долг переработчику); Зарплата (начисление → ведомость → РКО: остаток по сотруднику 0, касса; ПРОПУСК при дате начала расчёта позже даты теста); БезналичныеДеньги (поступление по реализации и списание поставщику: оба долга закрыты, счёт); ДополнительныеРеквизиты (реквизит и сведение идемпотентно, значения по имени); Отрасль (Строительство → 4 реквизита и константа, повтор 0, Торговля 0); НастройкиПрограммы (запись константы модулем менеджера панели настроек, признак ФО, часовые пояса, заголовок окна). Данные сценария заводятся заново в его транзакции, из базы — только организация и валюта учёта. E1 (2.0.15.2): ТехнологическиеКарты (границы дат, удаление материала, перезапись дня, заполнение выпуска, веса, отмена); ПереносТехнологическихКарт (даты и состав старой ТЧ, повтор без дублей, защита будущих карт, отмен и черновиков); СебестоимостьТехкарт (перенос → мультивыпуск 50/20 → новая рецептура → перепроведение без изменения старых сумм; ПРОПУСК без ФО «Производство»). Перенос вызывается для всей базы внутри откатываемой транзакции; ошибки прежних данных выявляются этим же прогоном. 2.0.15.3: ДатыТехкарты (день без времени для новой и существующей карты, отсутствие дублей, серверный запрет старой даты без изменения состава, будущая версия); ПоказателиТехкарты (последние цены, себестоимость, остатки, повторяющиеся материалы, дробный выпуск, характеристики, отрицательная маржа и отсутствие цен). E2 (2.0.15.7): СпособыПополненияЗапасов (умолчания шести типов, серверная страховка, сохранение значения Оба, миграция существующих элементов, пропуск групп и повторный запуск). E3 (2.0.15.8): КоммерческоеПредложение (Черновик и ручной статус, описание у каждой строки: разные описания строк одной номенклатуры, без переноса в карточку, вывод в печатную форму «Коммерческое предложение» (с 2.0.16.50 — собственная форма вместо Devis A4), заказ на основании, перенос шапки и строки, связь, статус Выигран, отказ заполнения заказа без смены статуса). E4 (2.0.15.9): ВидОперацииЗаказа (значение заполнения «Продажа», заполнение из отбора списка, страховка пустого вида при записи, смена вида у записанного заказа, по КП «Заказ клиента» — продажа, «Заказ клиента на производство» — «Производство» при включённой опции, независимо от номенклатуры предложения, представление заказа на производство и стандартное представление продажи, обработчик обновления и повторный запуск). E5 (2.0.15.13): МатериалыЗаказа (заполнение заказа на производство по техкартам с кодами строк, количеством за единицу и итогом, версией карты и упаковкой по опции; позиция без карты; повторный код; пересчёт и согласование при записи; отказ при разном составе одной продукции; смена номенклатуры и удаление строки; материалы по КП сразу; очистка у продажи; режим загрузки; ПРОПУСК без ФО «Производство»). E6 (2.0.15.14): ПроведениеЗаказа (регистрация версии карты при пустой колонке и отличии состава, дата версии — день проведения, версия становится действующей; повторное проведение без перезаписи карты (по версии данных); правка карты технологом не откатывается перепроведением; состав, равный действующей карте, без новой версии; новый состав перезаписывает карту дня; упаковка карты сохраняется, свёртка и перенос упаковки в обеих ветках опции; отказы без записи: продукция без материалов, пустой материал, материал = продукция, разные упаковки, будущая карта; закупаемый товар без материалов проводится; права ролей на карты; запрет смены вида у проведённого заказа и отмена проведения; проверка заполнения при записи из формы; заголовок формы; настоящий отказ проведения продажи последним шагом; ПРОПУСК без ФО «Производство»). E7 (2.0.15.15): ПотребностиПроизводства («Потребность» заказа на производство по продукции и перепроведение без дублей; закупки под продажу, непроведённый заказ и строка предварительного заказа без движений; ввод заказа поставщику по дефициту, явная продукция раньше распределения, излишек на последнюю продукцию; «Пришло» по коду строки и по «Заказано» заказа поставщику; ввод поступления по заказу клиента; сторно возвратов по своему поступлению; отчёт и «только дефицит»; перепроведение, отмена и повторное проведение; отказ записи изменённой потребности; отказ ввода без потребности последним шагом; ПРОПУСК без ФО «Производство»). E8 (2.0.15.20): СтадииЗаказа (стадия и индикатор расчёта и последней записи истории на каждом шаге; черновик и перепроведение без новых записей истории; заказ поставщику, два поступления, отмена второго и повторное проведение; выпуски 4 и 6; реализации частями, возврат и его отмена; оплата реализации, аванс «на основании заказа» без пересчёта и зачёт его во второй реализации, отмена оплаты; поздняя веха — отгрузка без закупок и выпуска; заказ без материалов и аванс по строке оснований; отмена проведения заказа со связанными документами; продажа, реализация по продаже и смена вида операции записью и вместе с отменой проведения без стадий; ПРОПУСК без ФО «Производство»). E9 (2.0.15.21): АвтовыпускПриОтгрузке (расчёт автовыпуска без записи — продукция, материалы с партией под заказ, продукция по техкарте, «ИзОстатка»; один автовыпуск на секунду раньше реализации; себестоимость автовыпуска и продажи по ФИФО, общая партия материала не тронута; к выпуску за вычетом свободного ручного выпуска, «ИзОстатка» в движениях и доле поступления стадии; перепроведение без дублей; отмена проведения, перенос и снятие пометки удаления; запрет правки автовыпуска и основания-реализации у ручного выпуска; выключенная константа и продажа без автовыпуска; граница по моменту времени; две реализации в одну секунду; серия продукции; отказ по нехватке материала; признак «создан автоматически» у автовыпуска, его отсутствие у ручного выпуска и у копии автовыпуска, обработчик обновления 2.0.15.42 проставляет признак без распроведения и без изменения движений, повтор идемпотентен (2.0.15.42); ПРОПУСК без ФО «Производство»). E10 (2.0.15.23): РучнойВыпуск (материалы ручного выпуска процедурой модуля менеджера, которую вызывает форма: версия карты на дату документа, одиночный режим берёт продукцию из шапки и заменяет посторонние строки, количество строки рассчитано, мультивыпуск по двум картам с кодами строк, себестоимость итогом, продукция без карты не меняет материалы; совет перезаполнить выпуски видит строку ручного мультивыпуска и не видит незаписанную строку продукции одиночного выпуска; ПРОПУСК без ФО «Производство»); в АвтовыпускПриОтгрузке — совет перезаполнить выпуски не учитывает автовыпуск и учитывает ручной выпуск рядом с ним. E11 (2.0.15.24): ДемоНабор (генератор демо-набора в транзакции прогона: стадии и индикаторы P1–P9 по схемам производства, статусы КП, заказов-продаж и договоров, автовыпуски, мультивыпуск, лиды и заявки; ПРОПУСК без ФО «Производство» или в первые 15 минут дня). СтадииЗаказа явно выключает константу автовыпуска. 2.0.15.28: АвторВОтветственного (перенос общего реквизита УдалитьАвторОбщий в пустой ответственный: проведённая реализация с неизменными движениями, непроведённая оплата без перепроведения связанной налоговой накладной, заполненный ответственный не меняется, проект конфигураций, автор справочника без ответственного сохраняется, повтор без записи). E12.1: сценарий АРМПроизводство — черновики и строки заказа на производство из рабочего места, кнопка «Статус», материалы и документы цепочки. E12.2: сценарий АРМЗакупки — заказы поставщику и поступления строками рабочего места: запись с проведением, распределение по изделиям, строки заказа поставщику, запреты, «Статус», удаление. E12.3a: сценарий АРМВыпускОтгрузка — выпуски и реализации строками рабочего места: материалы по карте, цена заказа, автовыпуск, «Статус», выпуск после отгрузки, удаление, выпуск по заказу. E12.3b: сценарий АРМПереработка — передачи в переработку строками рабочего места, продукция переработчика как выпуск в стадии и автовыпуске, запреты передачи со списанными партиями, поздний приход из переработки. E12.4: сценарий АРМПроизводство дополнен движением продукции и материалов по документам заказа — знак прихода, пустые колонки у непроведённого документа, количества в подсказке индикатора., СебестоимостьПродукции; РазворачиваниеТехкарты (разворачивание карты в глубину: три уровня до листьев, правило остановки, предел глубины и цикл с цепочкой, кэш в пределах вызова); ИерархияМатериаловЗаказа (дерево материалов заказа: заполнение и коды родителей, проведение не заводит новую версию карты, потребность и автовыпуск по листьям, удаление и копирование поддерева). S5-B (2.0.15.45): сценарий ПереработкаПоЗаказам расширен расчётом сырья по технологическим картам — процент потерь строки продукции из карты (новый реквизит ПоступлениеИзПереработки.ТЧГотоваяПродукция.ПроцентПотерь), расход как лимит на ГРУППУ строк остатка при материале в двух сериях, правка принятого количества с пересчётом сырья, порог дочистки (остаток ниже расчётных потерь уходит в то же поступление, движений в Убытки нет, партии второй ещё не вернувшейся передачи не тронуты), позиция без карты — весь остаток, доработка «передали продукцию — приняли её же», веса распределения себестоимости с процентом и без него. S9 (2.0.15.46): пересмотр АвтовыпускПриОтгрузке и АвтовыпускПриПередаче под правило «сначала свободный остаток склада, потом производство» — отгрузка шаг 11 (своя номенклатура: отгрузка целиком со склада без автовыпуска и без списания сырья, частичное покрытие и перепроведение, реализация задним числом не забирает остаток, нужный более поздним отгрузкам, себестоимость и остаток с величинами по обоим правилам, дефицит заказа не уменьшается взятым со склада), передача шаг 18 (передача задним числом не забирает уже переданный полуфабрикат); у шагов 3-4 и 7 отгрузки и 14 передачи числа прежние, обоснование новое. S6 (2.0.15.48): АРМПереработка расширен поступлением из переработки строкой рабочего места — новый проведённый документ по передаче, движения как через документ, вторая строка, услуги переработчика по строкам с НДС и «+ услуга переработки», удаление строки с переносом услуг, правки количества без задвоения и с остатком заказа без самого документа, запреты (непроведённая передача, не из ожидаемой, чужой заказ, раннее поступление при позднем, ручное сырьё), шапка услуг и ручной НДС, обработчик 2.0.15.48 и его повтор, «В работу» черновика, права оператора, пометка без строк. S7 (2.0.15.49): АРМПроизводство расширен подбором номенклатуры — типы подбора продукции (ГП, ПФ) и материалов (сырьё, ПФ, товар), без услуг и комплектов, отказ на неизвестное назначение; последние созданные по дате создания с пределом, без помеченных и чужих типов; жёсткий подбор продукции и мягкий материалов. Интерфейс подбора — ручная приёмка. ФункциональныеОпцииМеню (2.0.16.5): обработчики включения новых функциональных опций (существующая и новая база, повтор, регламентированный учёт по бухгалтерии), выбор мастера первого запуска, состав опций, проверка страны серии только с импортом. МенюЗакупок (2.0.16.6): группы раздела «Закупки» и права на них у четырёх ролей (у оператора производства раздела нет), группа «Импорт» в опции «Импорт», потребности производства в опции «Производство», реестр поступлений ушёл из Казначейства; «Просроченные долги поставщиков» — долг и дни просрочки по поступлению с истёкшим сроком, вариант «Основной» формируется. МенюПродаж (2.0.16.7): группы раздела «Продажи» и права на них у семи ролей («Цены» — без Казначея, PDV, оператора производства; «Розница» — Казначей, МенеджерПоЗакупкам, PDV), заявка на поиск в «Опте» один раз, «Опт» в четырёх опциях, «Розница» в своей, оплаты чеками — в альтернативных оплатах, налоговые отчёты вне «Продаж», реестр реализаций ушёл из Казначейства; «Просроченные долги покупателей» — долг и дни просрочки по продаже с истёкшим сроком, срок из карточки покупателя как у кредитного контроля, ненаступивший срок не показан, функция без ключа отдаёт весь долг (РМК), вариант «Основной» формируется. МенюСклада (2.0.16.9): группы раздела «Склад» в порядке Инвентаризация, Излишки и списания, Комплектация, Товары, Хранение и права на них у Кладовщика, Оператора, МенеджераПоЗакупкам; у Логиста — корень и «Хранение» без «Товаров», у оператора производства нет «Комплектации»; «Инвентаризация» в опции «Пересчёты», «Комплектация» — в своей, наборы упаковок — в опции «Упаковка»; перевозчики в «Хранении», штрихкоды в «Товарах», «Стоимость склада» не в «Бухгалтерии», «Ведомость по поступлениям» в «Закупках»; «Движения товара» / «Отчет по списанию товаров»: вариант формируется в табличный документ, списанное количество и себестоимость по товару со знаком расхода, поступление того же товара в вариант не попадает. МенюКазначействаИБухгалтерии (2.0.16.10): группы «Казначейства» (Оплаты клиентов — в опции) и «Бухгалтерии» (Регламентированный учёт — в опции), платёжные документы в корне Казначейства, перепроведение — в «Настройке» с правами Казначея, «Главной книги» нет, её разрез — вариантом «Расчетов с покупателями»; семь бухотчётов (с «Отчётом по проводкам», 2.0.16.11) формируются путём формы (ПодготовитьОтчет) на настоящей проводке операции регламентированного учёта без ошибки. МенюПрочихРазделов (2.0.16.10): «Переработчики» по признаку «Субподрядчик», группы ЗиК, CRM («Личный кабинет» в опции), «Настройки» («Сервисные операции»). 2.0.16.11 (в МенюПрочихРазделов): вход администратора в кабинет партнёра от имени покупателя и выход с очисткой корзины, «Что нового» и корень «Настройки» у девяти рабочих ролей, «Нехватка товара» в «Складе». 2.0.16.28: РабочееМестоЗакупок (рабочее место закупок без опции «Производство»: статус заказа поставщику до пагинации, индикатор поставки и оплаты по прямым платежам и через налоговую накладную, возврат, перенос предварительного заказа, страницы и отбор по статусу, данные нижних закладок). 2.0.16.29: РабочееМестоЗакупок расширен вводом — заказ поставщику строкой без заказа клиента, «К поступлению» (поступление на заказ с общей накладной, отказ строки пакета до записи и под блокировкой), строка в документ любой даты, «Изменить статус», защита перенесённых строк, валюта и курс поступления по валютному заказу, цена прайса в валюте заказа. 2.0.16.30: ПотребностьЗакупок (закладка «Потребность»: пополнение до минимума и дефицит заказа на производство, «Заказать» по поставщику и заказу клиента, повтор без дубля, прямое поступление закрывает дефицит, сводная строка с излишком в пополнение, раскладка по изделию с дефицитом). 2.0.16.31: ПотребностьЗакупок расширен тендером — предложения поставщикам, победитель, заказ у победителя в валюте предложения; ветка по текущему значению опции «Тендеры поставщиков». 2.0.16.32: СтанкиИОбслуживание — фонд времени станка по режиму и производственному календарю, обслуживание пишет «Загрузку станков», правило пересечений план/факт, отчёт «Простои станков» с внешним набором, состав опции «Учёт станков»; требование-накладная (сборка 2): вес и длительность, перемещение на склад станка партиями, выпуск со склада станка, недорасход и закрепление, «Вернуть в работу», отмена с возвратом и с оставлением материалов, запреты двойного выпуска, лимита заказа, переработки и автовыпуска. Закладка «Станки» (сборка 3): «Готовы к запуску», ближайшее окно мимо ТО и загрузок с шагом 15 минут, разбиение, перенос плана, затянувшаяся загрузка. Демо-набор (2.0.16.47): ДемоНаборПовтор — повторный запуск переиспользует по ключам, «неполные» кейсы без дублей, старый и прерванный набор; ДемоНаборОтказ — рабочий документ любого вида даёт отказ без записей; ДемоСтанки — блок учёта станков, 7 отчётов и закладка «Станки» непустые. Кнопка «Заполнить демо-данными» в «Компания и учёт» и фон — ручная приёмка (человек). 2.0.16.50: РедакцииКоммерческогоПредложения (номер редакции растёт только у отправленного КП при изменении содержимого, смена статуса и запись без изменений редакцию не создают; печать отправленной редакции из снимка — прежние наименование и логотип после их смены; печать выбранной редакции; возврат v1 даёт v3 с хешем v1; черновик правок — номер не растёт, на печати «v4 · черновик»; смена номера — новая редакция; копия без редакций; возврат с удалённой номенклатурой — пустая ссылка, НеНайдено, печать с прежним наименованием; КП, отправленное до учёта редакций, — v1 из базы при первой правке, в том числе с переводом в черновик; подложенный отложенный снимок при загрузке не пишется; печать v1 на каждом языке конфигурации — сумма прописью и надпись редакции на языке печати (2.0.16.51); редакции удаляются с документом; запись архива в обход документа отклоняется). 2.0.16.52: АналитикаЗагрузкиСтанков (фонд, занятость, свободное время, окно и дни двух недель, периоды 7 и 31 день, узкое место; риски запланированной, затянувшейся и незапущенной работы и очереди по черновику автоплана, выведенный станок, дефицит мощности по датам отгрузки; отчёт «План загрузки станков»). 2.0.16.54: ИнвентаризацияСтанков — документ на основании пересчёта «По станку» держит склад пересчёта после смены склада станка, другой станок — отказ записи. 2.0.16.55: ПростоиСтанковПланИФакт (план поверх факта только вне факта, план внутри факта не случай, MTTR полной длительностью ремонта через полночь, выведенный станок с работой и с затянувшимся требованием в отчёте, отборы отчёта: по виду обслуживания — в данные без потери фонда, по часам — не применяется, отборы группировки и строк таблицы выключаются, вариант компонуется; отказ программного проведения обслуживания с нулевым интервалом). 2.0.16.56: ИнвентаризацияСтанков — учётное пересчёта через Документы.ПересчётТоваров.ЗаполнитьУчетноеКоличество, заголовок «по станку». 2.0.16.57: ТребованиеЗапреты — лимит строки продукции (заказ 10 + 5, требование 8 по второй строке — запрет); АвтопланСтанков — окно не совпало с черновиком по окончанию или началу — не размещено; КарточкаНоменклатуры (минимумы нового товара по обоим измерениям, дубль артикула, ЗанятьШтрихкод, последняя строка свойства, цены карточки, группы отбора); СписокНоменклатуры (запрос списка: строка на товар, контекст, без минимумов складов; сведения панели); СписокНоменклатуры: иерархия через схему компоновки; КарточкаНоменклатуры: показатели шапки; КарточкаНоменклатуры: блоки карточки; СписокНоменклатуры: подбор по назначению, запрос выбора; ПереносСтарыхСвойств (перенос старых свойств номенклатуры в дополнительные реквизиты); ФирменнаяПечать (общий механизм фирменных печатных форм, снимки КП прежних форматов).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений). 2.0.16.62: КарточкаНоменклатуры дополнен показателями шапки карточки (ПоказателиКарточки: остаток, свободно, ниже минимума). 2.0.16.63: КарточкаНоменклатуры дополнен блоками карточки (ДанныеКарточки: где используется, остатки и свободно, штрихкоды). 2.0.16.64: СписокНоменклатуры — подбор по назначению и запрос выбора; смок открывает формы подбора и выбора номенклатуры с параметрами открытия. 2.0.16.65: ПроверитьГруппыОтбора — вид сравнения и ноль числового фильтра. 2.0.16.66: сценарий ПереносСтарыхСвойств (docs/plans/old-item-properties.md, сборка A).</t>
+          <t>Обновлено: 2026-10-10. Источник: docs/TESTING.md; E1: docs/plans/production-2mzl-e1-check.md; E3: коммерческое предложение; E4: вид операции заказа клиента; E5: материалы заказа на производство; E6: проведение заказа на производство; E7: потребности производства; E8: стадии заказа на производство; E9: автовыпуск при отгрузке; E10: ручной выпуск; E11: демо-набор; S4-A: признак автосоздания выпуска (docs/plans/production-subcontracting-s4.md); S4-B: автовыпуск полуфабриката при передаче в переработку (там же); S5-A: ожидаемая продукция по дереву заказа и отбор списания по заказу, сценарий ПереработкаПоЗаказам (docs/plans/production-subcontracting-s5.md); S5-B: процент потерь, расход сырья по картам и себестоимость поступления (docs/plans/production-subcontracting-s5.md, раздел «Сборка B»); S7: подборы номенклатуры (docs/plans/production-subcontracting-s7.md); 2.0.15.72: сценарий НалоговыеДокументыБезТовара; 2.0.15.73: сценарий ЦенаПослеУстановкиВКарточке; 2.0.16.22: сценарий ДокументыВВалюте (docs/plans/multicurrency.md); 2.0.16.23: сценарий ОплатыВВалюте (docs/plans/multicurrency-payments.md); 2.0.16.24: сценарий ЗаказыВВалюте (docs/plans/multicurrency-orders.md); 2.0.16.25: сценарий ВозвратыВВалюте (docs/plans/multicurrency-returns.md). 2.0.16.32: сценарий СтанкиИОбслуживание (docs/plans/machines.md, сборка 1). 2.0.16.33: сценарии ТребованиеНакладная, ТребованиеОтмена, ТребованиеЗапреты (там же, сборка 2). 2.0.16.34: сценарий ЗакладкаСтанков (там же, сборка 3). 2.0.16.35: сценарий ОтчетыСтанков (там же, сборка 4). 2.0.16.36–40: сценарии ЭффективностьСтанков, АвтопланСтанков, РастяжениеСтанков, ИнвентаризацияСтанков (docs/plans/machines-w5.md, волна 5). 2.0.16.42: сценарий ЗакладкаСтанков дополнен проверками «Занятости станков» — освободится, первое свободное окно, конец очереди за годовым горизонтом, затянувшаяся работа, отчёт вариантом по умолчанию (docs/plans/machines-occupancy.md). 2.0.16.46: сценарий ВыработкаПоНоменклатуре (docs/plans/machine-output-by-item.md); в СтанкиИОбслуживание — состав опции и группа «Производство / Станки» после 2.0.16.44. 2.0.16.47: сценарии ДемоНаборПовтор, ДемоНаборОтказ, ДемоСтанки (docs/plans/demo-data-button.md). 2.0.16.54: ИнвентаризацияСтанков дополнен шагом склада по пересчёту (docs/plans/machines-w6.md, волна 6). 2.0.16.55–58: сценарий ПростоиСтанковПланИФакт, дополнены ИнвентаризацияСтанков, ТребованиеЗапреты, АвтопланСтанков; сценарии станков — отдельным диспетчером СценарийСтанковПоИмени (docs/plans/machines-w6.md). 2.0.16.59: сценарий КарточкаНоменклатуры — запись карточки товара, ЗанятьШтрихкод, семантика свойства, группы ОтборыСписков (docs/plans/nomenclature-ui.md, этап 0); сценарии номенклатуры — диспетчером СценарийНоменклатурыПоИмени. 2.0.16.60: сценарий СписокНоменклатуры — запрос списка товаров из модуля менеджера (одна строка на товар при партиях, контекст «закупаемые», запрос без права на минимумы складов), сведения панели. 2.0.16.61: СписокНоменклатуры дополнен иерархией — узлы и отборы через схему компоновки с группами «Иерархия» и «Панель» (последняя строка свойства, «&lt;не задано&gt;», сведение, пересечение узла и панели, свойство панели, контекст, текст без сведений). 2.0.16.62: КарточкаНоменклатуры дополнен показателями шапки карточки (ПоказателиКарточки: остаток, свободно, ниже минимума). 2.0.16.63: КарточкаНоменклатуры дополнен блоками карточки (ДанныеКарточки: где используется, остатки и свободно, штрихкоды). 2.0.16.64: СписокНоменклатуры — подбор по назначению и запрос выбора; смок открывает формы подбора и выбора номенклатуры с параметрами открытия. 2.0.16.65: ПроверитьГруппыОтбора — вид сравнения и ноль числового фильтра. 2.0.16.66: сценарий ПереносСтарыхСвойств (docs/plans/old-item-properties.md, сборка A). 2.0.16.68: сценарий ФирменнаяПечать (docs/plans/branded-print.md, фаза 1), скрипт scripts/print-preview.sh.</t>
         </is>
       </c>
     </row>
